--- a/!!2026 Roll Sheets and Grades 7 David Cherry.xlsx
+++ b/!!2026 Roll Sheets and Grades 7 David Cherry.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\PerfectlyPracticalEnglish.GitHub.app_6_10_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\perfectly-practical-english.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7AA92EB-661B-4512-BBAB-8A758FFE8745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F4E80D-5AFD-4410-A795-BFDCC862E4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2230" yWindow="0" windowWidth="11480" windowHeight="9190" xr2:uid="{FDD99F55-0F01-4DEA-8581-43C2B56677F9}"/>
+    <workbookView xWindow="30" yWindow="6510" windowWidth="7970" windowHeight="3460" xr2:uid="{FDD99F55-0F01-4DEA-8581-43C2B56677F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Lookup" sheetId="5" r:id="rId1"/>
@@ -2029,7 +2029,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2052,11 +2052,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2212,10 +2227,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -2230,6 +2241,18 @@
     </xf>
     <xf numFmtId="10" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2545,324 +2568,331 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE04F95A-2A8F-479E-B3C6-F57DBD0999FF}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="B1:I20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="54"/>
-    <col min="2" max="2" width="7.7265625" style="51" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="54"/>
+    <col min="1" max="1" width="2.54296875" style="53" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" style="53"/>
+    <col min="3" max="3" width="2.1796875" style="53" customWidth="1"/>
+    <col min="4" max="4" width="8.1796875" style="51" customWidth="1"/>
+    <col min="5" max="9" width="8.7265625" style="60"/>
+    <col min="10" max="16384" width="8.7265625" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="53"/>
-      <c r="B1" s="52" t="str">
-        <f>IFERROR(INDEX(Grades!Q:Q,MATCH(A1,Grades!G:G,0)),"Student ID not found")</f>
-        <v>Student ID not found</v>
-      </c>
-      <c r="C1" s="54" t="s">
+    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="58">
+        <v>42889</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="52">
+        <f>IFERROR(INDEX(Grades!Q:Q,MATCH(B2,Grades!G:G,0)),"Enter ID")</f>
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="E2" s="60" t="s">
         <v>468</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="F2" s="60" t="s">
         <v>469</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="G2" s="60" t="s">
         <v>470</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="H2" s="60" t="s">
         <v>471</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="I2" s="60" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C2" s="54">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E3" s="60">
         <v>42889</v>
       </c>
-      <c r="D2" s="54">
+      <c r="F3" s="60">
         <v>42888</v>
       </c>
-      <c r="E2" s="54">
+      <c r="G3" s="60">
         <v>42973</v>
       </c>
-      <c r="F2" s="54">
+      <c r="H3" s="60">
         <v>43162</v>
       </c>
-      <c r="G2" s="54">
+      <c r="I3" s="60">
         <v>46948</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C3" s="54">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E4" s="60">
         <v>42956</v>
       </c>
-      <c r="D3" s="54">
+      <c r="F4" s="60">
         <v>42929</v>
       </c>
-      <c r="E3" s="54">
+      <c r="G4" s="60">
         <v>42983</v>
       </c>
-      <c r="F3" s="54">
+      <c r="H4" s="60">
         <v>43172</v>
       </c>
-      <c r="G3" s="54">
+      <c r="I4" s="60">
         <v>43045</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C4" s="54">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E5" s="60">
         <v>42974</v>
       </c>
-      <c r="D4" s="54">
+      <c r="F5" s="60">
         <v>42970</v>
       </c>
-      <c r="E4" s="54">
+      <c r="G5" s="60">
         <v>42998</v>
       </c>
-      <c r="F4" s="54">
+      <c r="H5" s="60">
         <v>43225</v>
       </c>
-      <c r="G4" s="54">
+      <c r="I5" s="60">
         <v>43055</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C5" s="54">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E6" s="60">
         <v>42978</v>
       </c>
-      <c r="D5" s="54">
+      <c r="F6" s="60">
         <v>42984</v>
       </c>
-      <c r="E5" s="54">
+      <c r="G6" s="60">
         <v>42999</v>
       </c>
-      <c r="F5" s="54">
+      <c r="H6" s="60">
         <v>43245</v>
       </c>
-      <c r="G5" s="54">
+      <c r="I6" s="60">
         <v>43063</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C6" s="54">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E7" s="60">
         <v>55555</v>
       </c>
-      <c r="D6" s="54">
+      <c r="F7" s="60">
         <v>42981</v>
       </c>
-      <c r="E6" s="54">
+      <c r="G7" s="60">
         <v>55555</v>
       </c>
-      <c r="F6" s="54">
+      <c r="H7" s="60">
         <v>55555</v>
       </c>
-      <c r="G6" s="54">
+      <c r="I7" s="60">
         <v>55555</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C7" s="54">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E8" s="60">
         <v>42979</v>
       </c>
-      <c r="D7" s="54">
+      <c r="F8" s="60">
         <v>55555</v>
       </c>
-      <c r="E7" s="54">
+      <c r="G8" s="60">
         <v>43023</v>
       </c>
-      <c r="F7" s="54">
+      <c r="H8" s="60">
         <v>43249</v>
       </c>
-      <c r="G7" s="54">
+      <c r="I8" s="60">
         <v>43093</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C8" s="54">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E9" s="60">
         <v>42995</v>
       </c>
-      <c r="D8" s="54">
+      <c r="F9" s="60">
         <v>42997</v>
       </c>
-      <c r="E8" s="54">
+      <c r="G9" s="60">
         <v>43032</v>
       </c>
-      <c r="F8" s="54">
+      <c r="H9" s="60">
         <v>43261</v>
       </c>
-      <c r="G8" s="54">
+      <c r="I9" s="60">
         <v>43113</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C9" s="54">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E10" s="60">
         <v>43015</v>
       </c>
-      <c r="D9" s="54">
+      <c r="F10" s="60">
         <v>43038</v>
       </c>
-      <c r="E9" s="54">
+      <c r="G10" s="60">
         <v>43034</v>
       </c>
-      <c r="F9" s="54">
+      <c r="H10" s="60">
         <v>43262</v>
       </c>
-      <c r="G9" s="54">
+      <c r="I10" s="60">
         <v>43128</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C10" s="54">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E11" s="60">
         <v>43017</v>
       </c>
-      <c r="D10" s="54">
+      <c r="F11" s="60">
         <v>43049</v>
       </c>
-      <c r="E10" s="54">
+      <c r="G11" s="60">
         <v>43056</v>
       </c>
-      <c r="F10" s="54">
+      <c r="H11" s="60">
         <v>43265</v>
       </c>
-      <c r="G10" s="54">
+      <c r="I11" s="60">
         <v>43143</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C11" s="54">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E12" s="60">
         <v>43150</v>
       </c>
-      <c r="D11" s="54">
+      <c r="F12" s="60">
         <v>43061</v>
       </c>
-      <c r="E11" s="54">
+      <c r="G12" s="60">
         <v>44558</v>
       </c>
-      <c r="F11" s="54">
+      <c r="H12" s="60">
         <v>46953</v>
       </c>
-      <c r="G11" s="54">
+      <c r="I12" s="60">
         <v>43144</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C12" s="54">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E13" s="60">
         <v>43163</v>
       </c>
-      <c r="D12" s="54">
+      <c r="F13" s="60">
         <v>43071</v>
       </c>
-      <c r="E12" s="54">
+      <c r="G13" s="60">
         <v>44563</v>
       </c>
-      <c r="F12" s="54">
+      <c r="H13" s="60">
         <v>46958</v>
       </c>
-      <c r="G12" s="54">
+      <c r="I13" s="60">
         <v>46496</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C13" s="54">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E14" s="60">
         <v>43173</v>
       </c>
-      <c r="D13" s="54">
+      <c r="F14" s="60">
         <v>43182</v>
       </c>
-      <c r="E13" s="54">
+      <c r="G14" s="60">
         <v>44589</v>
       </c>
-      <c r="F13" s="54">
+      <c r="H14" s="60">
         <v>47035</v>
       </c>
-      <c r="G13" s="54">
+      <c r="I14" s="60">
         <v>46923</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C14" s="54">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E15" s="60">
         <v>43217</v>
       </c>
-      <c r="D14" s="54">
+      <c r="F15" s="60">
         <v>43224</v>
       </c>
-      <c r="E14" s="54">
+      <c r="G15" s="60">
         <v>45165</v>
       </c>
-      <c r="F14" s="54">
+      <c r="H15" s="60">
         <v>47064</v>
       </c>
-      <c r="G14" s="54">
+      <c r="I15" s="60">
         <v>46924</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C15" s="54">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E16" s="60">
         <v>43220</v>
       </c>
-      <c r="D15" s="54">
+      <c r="F16" s="60">
         <v>43251</v>
       </c>
-      <c r="E15" s="54">
+      <c r="G16" s="60">
         <v>45875</v>
       </c>
-      <c r="F15" s="54">
+      <c r="H16" s="60">
         <v>47074</v>
       </c>
-      <c r="G15" s="54">
+      <c r="I16" s="60">
         <v>46930</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C16" s="54">
+    <row r="17" spans="5:9" x14ac:dyDescent="0.35">
+      <c r="E17" s="60">
         <v>55555</v>
       </c>
-      <c r="D16" s="54">
+      <c r="F17" s="60">
         <v>43255</v>
       </c>
-      <c r="E16" s="54">
+      <c r="G17" s="60">
         <v>45875</v>
       </c>
-      <c r="F16" s="54">
+      <c r="H17" s="60">
         <v>55555</v>
       </c>
-      <c r="G16" s="54">
+      <c r="I17" s="60">
         <v>55555</v>
       </c>
     </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C17" s="54">
+    <row r="18" spans="5:9" x14ac:dyDescent="0.35">
+      <c r="E18" s="60">
         <v>43226</v>
       </c>
-      <c r="D17" s="54">
+      <c r="F18" s="60">
         <v>55555</v>
       </c>
-      <c r="E17" s="54">
+      <c r="G18" s="60">
         <v>55555</v>
       </c>
-      <c r="F17" s="54">
+      <c r="H18" s="60">
         <v>47086</v>
       </c>
-      <c r="G17" s="54">
+      <c r="I18" s="60">
         <v>46934</v>
       </c>
     </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="D18" s="54">
+    <row r="19" spans="5:9" x14ac:dyDescent="0.35">
+      <c r="F19" s="60">
         <v>43427</v>
       </c>
-      <c r="E18" s="54">
+      <c r="G19" s="60">
         <v>45892</v>
       </c>
-      <c r="G18" s="54">
+      <c r="I19" s="60">
         <v>46939</v>
       </c>
     </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="E19" s="54">
+    <row r="20" spans="5:9" x14ac:dyDescent="0.35">
+      <c r="G20" s="60">
         <v>46491</v>
       </c>
-      <c r="G19" s="54">
+      <c r="I20" s="60">
         <v>47124</v>
       </c>
     </row>
@@ -7445,10 +7475,10 @@
       <c r="N3" s="17">
         <v>-9</v>
       </c>
-      <c r="O3" s="55">
+      <c r="O3" s="54">
         <v>21</v>
       </c>
-      <c r="P3" s="56">
+      <c r="P3" s="55">
         <v>0.7</v>
       </c>
     </row>
@@ -7627,10 +7657,10 @@
       <c r="N7" s="17">
         <v>-7</v>
       </c>
-      <c r="O7" s="55">
+      <c r="O7" s="54">
         <v>23</v>
       </c>
-      <c r="P7" s="56">
+      <c r="P7" s="55">
         <v>0.76700000000000002</v>
       </c>
     </row>
@@ -7821,10 +7851,10 @@
       <c r="N11" s="17">
         <v>-10</v>
       </c>
-      <c r="O11" s="55">
+      <c r="O11" s="54">
         <v>20</v>
       </c>
-      <c r="P11" s="56">
+      <c r="P11" s="55">
         <v>0.66700000000000004</v>
       </c>
     </row>
@@ -8368,7 +8398,7 @@
       <c r="N23" s="17">
         <v>-5</v>
       </c>
-      <c r="O23" s="55">
+      <c r="O23" s="54">
         <v>25</v>
       </c>
       <c r="P23" s="50">
@@ -8928,10 +8958,10 @@
       <c r="N35" s="17">
         <v>-8</v>
       </c>
-      <c r="O35" s="55">
+      <c r="O35" s="54">
         <v>22</v>
       </c>
-      <c r="P35" s="56">
+      <c r="P35" s="55">
         <v>0.73299999999999998</v>
       </c>
     </row>
@@ -9009,10 +9039,10 @@
       <c r="N37" s="17">
         <v>-26</v>
       </c>
-      <c r="O37" s="55">
+      <c r="O37" s="54">
         <v>4</v>
       </c>
-      <c r="P37" s="56">
+      <c r="P37" s="55">
         <v>0.13300000000000001</v>
       </c>
     </row>
@@ -9109,7 +9139,7 @@
       <c r="N39" s="17">
         <v>-15</v>
       </c>
-      <c r="O39" s="55">
+      <c r="O39" s="54">
         <v>15</v>
       </c>
       <c r="P39" s="50">
@@ -9159,10 +9189,10 @@
       <c r="N40" s="17">
         <v>-8</v>
       </c>
-      <c r="O40" s="55">
+      <c r="O40" s="54">
         <v>22</v>
       </c>
-      <c r="P40" s="56">
+      <c r="P40" s="55">
         <v>0.73299999999999998</v>
       </c>
     </row>
@@ -9333,10 +9363,10 @@
       <c r="N44" s="17">
         <v>-18</v>
       </c>
-      <c r="O44" s="55">
+      <c r="O44" s="54">
         <v>12</v>
       </c>
-      <c r="P44" s="56">
+      <c r="P44" s="55">
         <v>0.4</v>
       </c>
     </row>
@@ -9383,10 +9413,10 @@
       <c r="N45" s="17">
         <v>-7</v>
       </c>
-      <c r="O45" s="55">
+      <c r="O45" s="54">
         <v>23</v>
       </c>
-      <c r="P45" s="56">
+      <c r="P45" s="55">
         <v>0.76700000000000002</v>
       </c>
     </row>
@@ -9533,10 +9563,10 @@
       <c r="N48" s="17">
         <v>-23</v>
       </c>
-      <c r="O48" s="55">
+      <c r="O48" s="54">
         <v>7</v>
       </c>
-      <c r="P48" s="56">
+      <c r="P48" s="55">
         <v>0.23300000000000001</v>
       </c>
     </row>
@@ -9633,10 +9663,10 @@
       <c r="N50" s="17">
         <v>-23</v>
       </c>
-      <c r="O50" s="55">
+      <c r="O50" s="54">
         <v>7</v>
       </c>
-      <c r="P50" s="56">
+      <c r="P50" s="55">
         <v>0.23300000000000001</v>
       </c>
     </row>
@@ -9715,10 +9745,10 @@
       <c r="N52" s="17">
         <v>17</v>
       </c>
-      <c r="O52" s="55">
+      <c r="O52" s="54">
         <v>17</v>
       </c>
-      <c r="P52" s="56">
+      <c r="P52" s="55">
         <v>0.56699999999999995</v>
       </c>
     </row>
@@ -9765,10 +9795,10 @@
       <c r="N53" s="17">
         <v>-7</v>
       </c>
-      <c r="O53" s="55">
+      <c r="O53" s="54">
         <v>23</v>
       </c>
-      <c r="P53" s="56">
+      <c r="P53" s="55">
         <v>0.76700000000000002</v>
       </c>
     </row>
@@ -9846,10 +9876,10 @@
       <c r="N55" s="17">
         <v>-7</v>
       </c>
-      <c r="O55" s="55">
+      <c r="O55" s="54">
         <v>23</v>
       </c>
-      <c r="P55" s="56">
+      <c r="P55" s="55">
         <v>0.76700000000000002</v>
       </c>
     </row>
@@ -9946,10 +9976,10 @@
       <c r="N57" s="17">
         <v>-22</v>
       </c>
-      <c r="O57" s="55">
+      <c r="O57" s="54">
         <v>8</v>
       </c>
-      <c r="P57" s="56">
+      <c r="P57" s="55">
         <v>0.26700000000000002</v>
       </c>
     </row>
@@ -9996,10 +10026,10 @@
       <c r="N58" s="17">
         <v>-10</v>
       </c>
-      <c r="O58" s="55">
+      <c r="O58" s="54">
         <v>20</v>
       </c>
-      <c r="P58" s="56">
+      <c r="P58" s="55">
         <v>0.66700000000000004</v>
       </c>
     </row>
@@ -10128,10 +10158,10 @@
       <c r="N61" s="17">
         <v>-7</v>
       </c>
-      <c r="O61" s="55">
+      <c r="O61" s="54">
         <v>23</v>
       </c>
-      <c r="P61" s="56">
+      <c r="P61" s="55">
         <v>0.76700000000000002</v>
       </c>
     </row>
@@ -10228,10 +10258,10 @@
       <c r="N63" s="17">
         <v>-8</v>
       </c>
-      <c r="O63" s="55">
+      <c r="O63" s="54">
         <v>22</v>
       </c>
-      <c r="P63" s="56">
+      <c r="P63" s="55">
         <v>0.73299999999999998</v>
       </c>
     </row>
@@ -10376,10 +10406,10 @@
       <c r="N66" s="17">
         <v>-22</v>
       </c>
-      <c r="O66" s="55">
+      <c r="O66" s="54">
         <v>8</v>
       </c>
-      <c r="P66" s="56">
+      <c r="P66" s="55">
         <v>0.26700000000000002</v>
       </c>
     </row>
@@ -10426,10 +10456,10 @@
       <c r="N67" s="17">
         <v>-15</v>
       </c>
-      <c r="O67" s="55">
+      <c r="O67" s="54">
         <v>15</v>
       </c>
-      <c r="P67" s="56">
+      <c r="P67" s="55">
         <v>0.5</v>
       </c>
     </row>
@@ -10476,10 +10506,10 @@
       <c r="N68" s="17">
         <v>-12</v>
       </c>
-      <c r="O68" s="55">
+      <c r="O68" s="54">
         <v>18</v>
       </c>
-      <c r="P68" s="56">
+      <c r="P68" s="55">
         <v>0.6</v>
       </c>
     </row>
@@ -10558,10 +10588,10 @@
       <c r="N70" s="17">
         <v>-26</v>
       </c>
-      <c r="O70" s="55">
+      <c r="O70" s="54">
         <v>4</v>
       </c>
-      <c r="P70" s="56">
+      <c r="P70" s="55">
         <v>0.13300000000000001</v>
       </c>
     </row>
@@ -10911,10 +10941,10 @@
       <c r="N78" s="17">
         <v>-9</v>
       </c>
-      <c r="O78" s="55">
+      <c r="O78" s="54">
         <v>21</v>
       </c>
-      <c r="P78" s="56">
+      <c r="P78" s="55">
         <v>0.7</v>
       </c>
     </row>
@@ -10961,10 +10991,10 @@
       <c r="N79" s="17">
         <v>-10</v>
       </c>
-      <c r="O79" s="55">
+      <c r="O79" s="54">
         <v>20</v>
       </c>
-      <c r="P79" s="56">
+      <c r="P79" s="55">
         <v>0.66700000000000004</v>
       </c>
     </row>
@@ -11011,10 +11041,10 @@
       <c r="N80" s="17">
         <v>-19</v>
       </c>
-      <c r="O80" s="55">
+      <c r="O80" s="54">
         <v>11</v>
       </c>
-      <c r="P80" s="56">
+      <c r="P80" s="55">
         <v>0.36699999999999999</v>
       </c>
     </row>
@@ -11111,10 +11141,10 @@
       <c r="N82" s="17">
         <v>-15</v>
       </c>
-      <c r="O82" s="55">
+      <c r="O82" s="54">
         <v>15</v>
       </c>
-      <c r="P82" s="56">
+      <c r="P82" s="55">
         <v>0.5</v>
       </c>
     </row>
@@ -11253,10 +11283,10 @@
       <c r="N85" s="17">
         <v>-14</v>
       </c>
-      <c r="O85" s="55">
+      <c r="O85" s="54">
         <v>16</v>
       </c>
-      <c r="P85" s="56">
+      <c r="P85" s="55">
         <v>0.53300000000000003</v>
       </c>
     </row>
@@ -11386,10 +11416,10 @@
         <f>-G189+#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="O88" s="55">
+      <c r="O88" s="54">
         <v>0</v>
       </c>
-      <c r="P88" s="56">
+      <c r="P88" s="55">
         <v>0</v>
       </c>
     </row>
@@ -11424,10 +11454,10 @@
         <v>456</v>
       </c>
       <c r="N89" s="17"/>
-      <c r="O89" s="55">
+      <c r="O89" s="54">
         <v>0</v>
       </c>
-      <c r="P89" s="56">
+      <c r="P89" s="55">
         <v>0</v>
       </c>
     </row>
@@ -11493,10 +11523,10 @@
       <c r="N1" s="17">
         <v>-9</v>
       </c>
-      <c r="O1" s="57">
+      <c r="O1" s="56">
         <v>21</v>
       </c>
-      <c r="P1" s="58">
+      <c r="P1" s="57">
         <v>0.7</v>
       </c>
     </row>
@@ -11543,10 +11573,10 @@
       <c r="N2" s="17">
         <v>-7</v>
       </c>
-      <c r="O2" s="55">
+      <c r="O2" s="54">
         <v>23</v>
       </c>
-      <c r="P2" s="56">
+      <c r="P2" s="55">
         <v>0.76700000000000002</v>
       </c>
     </row>
@@ -11593,10 +11623,10 @@
       <c r="N3" s="17">
         <v>-10</v>
       </c>
-      <c r="O3" s="55">
+      <c r="O3" s="54">
         <v>20</v>
       </c>
-      <c r="P3" s="56">
+      <c r="P3" s="55">
         <v>0.66700000000000004</v>
       </c>
     </row>
@@ -11643,10 +11673,10 @@
       <c r="N4" s="17">
         <v>-8</v>
       </c>
-      <c r="O4" s="55">
+      <c r="O4" s="54">
         <v>22</v>
       </c>
-      <c r="P4" s="56">
+      <c r="P4" s="55">
         <v>0.73299999999999998</v>
       </c>
     </row>
@@ -11693,10 +11723,10 @@
       <c r="N5" s="17">
         <v>-26</v>
       </c>
-      <c r="O5" s="55">
+      <c r="O5" s="54">
         <v>4</v>
       </c>
-      <c r="P5" s="56">
+      <c r="P5" s="55">
         <v>0.13300000000000001</v>
       </c>
     </row>
@@ -11743,10 +11773,10 @@
       <c r="N6" s="17">
         <v>-8</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="54">
         <v>22</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="55">
         <v>0.73299999999999998</v>
       </c>
     </row>
@@ -11793,10 +11823,10 @@
       <c r="N7" s="17">
         <v>-18</v>
       </c>
-      <c r="O7" s="55">
+      <c r="O7" s="54">
         <v>12</v>
       </c>
-      <c r="P7" s="56">
+      <c r="P7" s="55">
         <v>0.4</v>
       </c>
     </row>
@@ -11843,10 +11873,10 @@
       <c r="N8" s="17">
         <v>-7</v>
       </c>
-      <c r="O8" s="55">
+      <c r="O8" s="54">
         <v>23</v>
       </c>
-      <c r="P8" s="56">
+      <c r="P8" s="55">
         <v>0.76700000000000002</v>
       </c>
     </row>
@@ -11893,10 +11923,10 @@
       <c r="N9" s="17">
         <v>-23</v>
       </c>
-      <c r="O9" s="55">
+      <c r="O9" s="54">
         <v>7</v>
       </c>
-      <c r="P9" s="56">
+      <c r="P9" s="55">
         <v>0.23300000000000001</v>
       </c>
     </row>
@@ -11943,10 +11973,10 @@
       <c r="N10" s="17">
         <v>-23</v>
       </c>
-      <c r="O10" s="55">
+      <c r="O10" s="54">
         <v>7</v>
       </c>
-      <c r="P10" s="56">
+      <c r="P10" s="55">
         <v>0.23300000000000001</v>
       </c>
     </row>
@@ -11993,10 +12023,10 @@
       <c r="N11" s="17">
         <v>17</v>
       </c>
-      <c r="O11" s="55">
+      <c r="O11" s="54">
         <v>17</v>
       </c>
-      <c r="P11" s="56">
+      <c r="P11" s="55">
         <v>0.56699999999999995</v>
       </c>
     </row>
@@ -12043,10 +12073,10 @@
       <c r="N12" s="17">
         <v>-7</v>
       </c>
-      <c r="O12" s="55">
+      <c r="O12" s="54">
         <v>23</v>
       </c>
-      <c r="P12" s="56">
+      <c r="P12" s="55">
         <v>0.76700000000000002</v>
       </c>
     </row>
@@ -12093,10 +12123,10 @@
       <c r="N13" s="17">
         <v>-7</v>
       </c>
-      <c r="O13" s="55">
+      <c r="O13" s="54">
         <v>23</v>
       </c>
-      <c r="P13" s="56">
+      <c r="P13" s="55">
         <v>0.76700000000000002</v>
       </c>
     </row>
@@ -12143,10 +12173,10 @@
       <c r="N14" s="17">
         <v>-22</v>
       </c>
-      <c r="O14" s="55">
+      <c r="O14" s="54">
         <v>8</v>
       </c>
-      <c r="P14" s="56">
+      <c r="P14" s="55">
         <v>0.26700000000000002</v>
       </c>
     </row>
@@ -12193,10 +12223,10 @@
       <c r="N15" s="17">
         <v>-10</v>
       </c>
-      <c r="O15" s="55">
+      <c r="O15" s="54">
         <v>20</v>
       </c>
-      <c r="P15" s="56">
+      <c r="P15" s="55">
         <v>0.66700000000000004</v>
       </c>
     </row>
@@ -12243,10 +12273,10 @@
       <c r="N16" s="17">
         <v>-7</v>
       </c>
-      <c r="O16" s="55">
+      <c r="O16" s="54">
         <v>23</v>
       </c>
-      <c r="P16" s="56">
+      <c r="P16" s="55">
         <v>0.76700000000000002</v>
       </c>
     </row>
@@ -12293,10 +12323,10 @@
       <c r="N17" s="17">
         <v>-8</v>
       </c>
-      <c r="O17" s="55">
+      <c r="O17" s="54">
         <v>22</v>
       </c>
-      <c r="P17" s="56">
+      <c r="P17" s="55">
         <v>0.73299999999999998</v>
       </c>
     </row>
@@ -12341,10 +12371,10 @@
       <c r="N18" s="17">
         <v>-22</v>
       </c>
-      <c r="O18" s="55">
+      <c r="O18" s="54">
         <v>8</v>
       </c>
-      <c r="P18" s="56">
+      <c r="P18" s="55">
         <v>0.26700000000000002</v>
       </c>
     </row>
@@ -12391,10 +12421,10 @@
       <c r="N19" s="17">
         <v>-15</v>
       </c>
-      <c r="O19" s="55">
+      <c r="O19" s="54">
         <v>15</v>
       </c>
-      <c r="P19" s="56">
+      <c r="P19" s="55">
         <v>0.5</v>
       </c>
     </row>
@@ -12441,10 +12471,10 @@
       <c r="N20" s="17">
         <v>-12</v>
       </c>
-      <c r="O20" s="55">
+      <c r="O20" s="54">
         <v>18</v>
       </c>
-      <c r="P20" s="56">
+      <c r="P20" s="55">
         <v>0.6</v>
       </c>
     </row>
@@ -12491,10 +12521,10 @@
       <c r="N21" s="17">
         <v>-26</v>
       </c>
-      <c r="O21" s="55">
+      <c r="O21" s="54">
         <v>4</v>
       </c>
-      <c r="P21" s="56">
+      <c r="P21" s="55">
         <v>0.13300000000000001</v>
       </c>
     </row>
@@ -12541,10 +12571,10 @@
       <c r="N22" s="17">
         <v>-9</v>
       </c>
-      <c r="O22" s="55">
+      <c r="O22" s="54">
         <v>21</v>
       </c>
-      <c r="P22" s="56">
+      <c r="P22" s="55">
         <v>0.7</v>
       </c>
     </row>
@@ -12591,10 +12621,10 @@
       <c r="N23" s="17">
         <v>-10</v>
       </c>
-      <c r="O23" s="55">
+      <c r="O23" s="54">
         <v>20</v>
       </c>
-      <c r="P23" s="56">
+      <c r="P23" s="55">
         <v>0.66700000000000004</v>
       </c>
     </row>
@@ -12641,10 +12671,10 @@
       <c r="N24" s="17">
         <v>-19</v>
       </c>
-      <c r="O24" s="55">
+      <c r="O24" s="54">
         <v>11</v>
       </c>
-      <c r="P24" s="56">
+      <c r="P24" s="55">
         <v>0.36699999999999999</v>
       </c>
     </row>
@@ -12691,10 +12721,10 @@
       <c r="N25" s="17">
         <v>-15</v>
       </c>
-      <c r="O25" s="55">
+      <c r="O25" s="54">
         <v>15</v>
       </c>
-      <c r="P25" s="56">
+      <c r="P25" s="55">
         <v>0.5</v>
       </c>
     </row>
@@ -12741,10 +12771,10 @@
       <c r="N26" s="17">
         <v>-14</v>
       </c>
-      <c r="O26" s="55">
+      <c r="O26" s="54">
         <v>16</v>
       </c>
-      <c r="P26" s="56">
+      <c r="P26" s="55">
         <v>0.53300000000000003</v>
       </c>
     </row>
@@ -12792,10 +12822,10 @@
         <f>-G128+#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="O27" s="55">
+      <c r="O27" s="54">
         <v>0</v>
       </c>
-      <c r="P27" s="56">
+      <c r="P27" s="55">
         <v>0</v>
       </c>
     </row>
@@ -12830,10 +12860,10 @@
         <v>456</v>
       </c>
       <c r="N28" s="17"/>
-      <c r="O28" s="55">
+      <c r="O28" s="54">
         <v>0</v>
       </c>
-      <c r="P28" s="56">
+      <c r="P28" s="55">
         <v>0</v>
       </c>
     </row>

--- a/!!2026 Roll Sheets and Grades 7 David Cherry.xlsx
+++ b/!!2026 Roll Sheets and Grades 7 David Cherry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\perfectly-practical-english.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F4E80D-5AFD-4410-A795-BFDCC862E4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329C6488-BCA5-4509-979B-3BDE4C19CB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="6510" windowWidth="7970" windowHeight="3460" xr2:uid="{FDD99F55-0F01-4DEA-8581-43C2B56677F9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{FDD99F55-0F01-4DEA-8581-43C2B56677F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Lookup" sheetId="5" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2551" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2551" uniqueCount="475">
   <si>
     <t>Matthayom  11.1</t>
   </si>
@@ -1844,6 +1844,9 @@
   </si>
   <si>
     <t>Seat 18.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -2246,7 +2249,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -6447,7 +6450,7 @@
         <v>16.2</v>
       </c>
       <c r="I72" s="36" t="s">
-        <v>398</v>
+        <v>474</v>
       </c>
       <c r="J72" s="36" t="s">
         <v>399</v>
